--- a/filer_2/26211425_westpack_a_s.xlsx
+++ b/filer_2/26211425_westpack_a_s.xlsx
@@ -4546,54 +4546,54 @@
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Overskudsgrad, %</t>
+          <t>Overskudsgrad (af bruttofortjeneste), %</t>
         </is>
       </c>
       <c r="B90" s="14">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$8*100,"")</f>
         <v/>
       </c>
       <c r="C90" s="14">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$8*100,"")</f>
         <v/>
       </c>
       <c r="D90" s="14">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$8*100,"")</f>
         <v/>
       </c>
       <c r="E90" s="14">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$8*100,"")</f>
         <v/>
       </c>
       <c r="F90" s="14">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$8*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>Aktivernes omsætningshastighed, gange</t>
+          <t>Aktivernes omsætningshastighed (af bruttofortjeneste), gange</t>
         </is>
       </c>
       <c r="B91" s="13">
-        <f>IFERROR($B$4/$B$52,"")</f>
+        <f>IFERROR($B$8/$B$52,"")</f>
         <v/>
       </c>
       <c r="C91" s="13">
-        <f>IFERROR($C$4/$C$52,"")</f>
+        <f>IFERROR($C$8/$C$52,"")</f>
         <v/>
       </c>
       <c r="D91" s="13">
-        <f>IFERROR($D$4/$D$52,"")</f>
+        <f>IFERROR($D$8/$D$52,"")</f>
         <v/>
       </c>
       <c r="E91" s="13">
-        <f>IFERROR($E$4/$E$52,"")</f>
+        <f>IFERROR($E$8/$E$52,"")</f>
         <v/>
       </c>
       <c r="F91" s="13">
-        <f>IFERROR($F$4/$F$52,"")</f>
+        <f>IFERROR($F$8/$F$52,"")</f>
         <v/>
       </c>
     </row>
@@ -6764,20 +6764,20 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>SUM(B5:B8)</f>
+        <f>IF(COUNT('res_raw_26211425'!$F$2,'res_raw_26211425'!$F$3,'res_raw_26211425'!$F$4,'res_raw_26211425'!$F$5)=0,'res_raw_26211425'!$F$6,SUM(B5:B8))</f>
         <v/>
       </c>
       <c r="C9" s="27">
-        <f>SUM(C5:C8)</f>
+        <f>IF(COUNT('res_raw_26211425'!$E$2,'res_raw_26211425'!$E$3,'res_raw_26211425'!$E$4,'res_raw_26211425'!$E$5)=0,'res_raw_26211425'!$E$6,SUM(C5:C8))</f>
         <v/>
       </c>
       <c r="D9" s="27">
-        <f>SUM(D5:D8)</f>
+        <f>IF(COUNT('res_raw_26211425'!$D$2,'res_raw_26211425'!$D$3,'res_raw_26211425'!$D$4,'res_raw_26211425'!$D$5)=0,'res_raw_26211425'!$D$6,SUM(D5:D8))</f>
         <v/>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>Beregnet: Nettoomsætning + Andre driftsindt. − Vareforbrug − Andre ext. omk.</t>
+          <t>Beregnet: Nettoomsætning + Andre driftsindt. − Vareforbrug − Andre ext. omk. Er komponenterne ikke indberettet, vises rapporteret bruttoresultat (fsa:GrossResult) direkte.</t>
         </is>
       </c>
     </row>
@@ -7249,19 +7249,19 @@
     <row r="34">
       <c r="A34" s="23" t="inlineStr">
         <is>
-          <t>Overskudsgrad, %</t>
+          <t>Overskudsgrad (af bruttofortjeneste), %</t>
         </is>
       </c>
       <c r="B34" s="30">
-        <f>IFERROR((B13+B14)/B5*100,"")</f>
+        <f>IFERROR((B13+B14)/B9*100,"")</f>
         <v/>
       </c>
       <c r="C34" s="30">
-        <f>IFERROR((C13+C14)/C5*100,"")</f>
+        <f>IFERROR((C13+C14)/C9*100,"")</f>
         <v/>
       </c>
       <c r="D34" s="30">
-        <f>IFERROR((D13+D14)/D5*100,"")</f>
+        <f>IFERROR((D13+D14)/D9*100,"")</f>
         <v/>
       </c>
       <c r="F34" s="29" t="n"/>
@@ -7269,19 +7269,19 @@
     <row r="35">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>Aktivernes omsætningshastighed, gange</t>
+          <t>Aktivernes omsætningshastighed (af bruttofortjeneste), gange</t>
         </is>
       </c>
       <c r="B35" s="30">
-        <f>IFERROR(B5/B21,"")</f>
+        <f>IFERROR(B9/B21,"")</f>
         <v/>
       </c>
       <c r="C35" s="30">
-        <f>IFERROR(C5/C21,"")</f>
+        <f>IFERROR(C9/C21,"")</f>
         <v/>
       </c>
       <c r="D35" s="30">
-        <f>IFERROR(D5/D21,"")</f>
+        <f>IFERROR(D9/D21,"")</f>
         <v/>
       </c>
       <c r="F35" s="29" t="n"/>
@@ -7367,19 +7367,19 @@
     <row r="41">
       <c r="A41" s="23" t="inlineStr">
         <is>
-          <t>Nettoomsætning</t>
+          <t>Bruttofortjeneste</t>
         </is>
       </c>
       <c r="B41" s="31">
-        <f>IFERROR(B5/$D5*100,"")</f>
+        <f>IFERROR(B9/$D9*100,"")</f>
         <v/>
       </c>
       <c r="C41" s="31">
-        <f>IFERROR(C5/$D5*100,"")</f>
+        <f>IFERROR(C9/$D9*100,"")</f>
         <v/>
       </c>
       <c r="D41" s="31">
-        <f>IFERROR(D5/$D5*100,"")</f>
+        <f>IFERROR(D9/$D9*100,"")</f>
         <v/>
       </c>
       <c r="F41" s="29" t="n"/>
@@ -7485,19 +7485,19 @@
     <row r="48">
       <c r="A48" s="23" t="inlineStr">
         <is>
-          <t>Nettoomsætning</t>
+          <t>Bruttofortjeneste</t>
         </is>
       </c>
       <c r="B48" s="31">
-        <f>IFERROR(B5*100/$D5,"")</f>
+        <f>IFERROR(B9*100/$D9,"")</f>
         <v/>
       </c>
       <c r="C48" s="31">
-        <f>IFERROR(C5*100/$D5,"")</f>
+        <f>IFERROR(C9*100/$D9,"")</f>
         <v/>
       </c>
       <c r="D48" s="31">
-        <f>IFERROR(D5*100/$D5,"")</f>
+        <f>IFERROR(D9*100/$D9,"")</f>
         <v/>
       </c>
       <c r="F48" s="29" t="n"/>

--- a/filer_2/26211425_westpack_a_s.xlsx
+++ b/filer_2/26211425_westpack_a_s.xlsx
@@ -6764,15 +6764,15 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>IF(COUNT('res_raw_26211425'!$F$2,'res_raw_26211425'!$F$3,'res_raw_26211425'!$F$4,'res_raw_26211425'!$F$5)=0,'res_raw_26211425'!$F$6,SUM(B5:B8))</f>
+        <f>IF(ABS((SUM(B5:B8))-'res_raw_26211425'!$F$6)&lt;=2,SUM(B5:B8),'res_raw_26211425'!$F$6)</f>
         <v/>
       </c>
       <c r="C9" s="27">
-        <f>IF(COUNT('res_raw_26211425'!$E$2,'res_raw_26211425'!$E$3,'res_raw_26211425'!$E$4,'res_raw_26211425'!$E$5)=0,'res_raw_26211425'!$E$6,SUM(C5:C8))</f>
+        <f>IF(ABS((SUM(C5:C8))-'res_raw_26211425'!$E$6)&lt;=2,SUM(C5:C8),'res_raw_26211425'!$E$6)</f>
         <v/>
       </c>
       <c r="D9" s="27">
-        <f>IF(COUNT('res_raw_26211425'!$D$2,'res_raw_26211425'!$D$3,'res_raw_26211425'!$D$4,'res_raw_26211425'!$D$5)=0,'res_raw_26211425'!$D$6,SUM(D5:D8))</f>
+        <f>IF(ABS((SUM(D5:D8))-'res_raw_26211425'!$D$6)&lt;=2,SUM(D5:D8),'res_raw_26211425'!$D$6)</f>
         <v/>
       </c>
       <c r="F9" s="28" t="inlineStr">
@@ -6860,15 +6860,15 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(B9:B12)</f>
+        <f>IF(ABS((SUM(B9:B12))-'res_raw_26211425'!$F$11)&lt;=2,SUM(B9:B12),'res_raw_26211425'!$F$11)</f>
         <v/>
       </c>
       <c r="C13" s="27">
-        <f>SUM(C9:C12)</f>
+        <f>IF(ABS((SUM(C9:C12))-'res_raw_26211425'!$E$11)&lt;=2,SUM(C9:C12),'res_raw_26211425'!$E$11)</f>
         <v/>
       </c>
       <c r="D13" s="27">
-        <f>SUM(D9:D12)</f>
+        <f>IF(ABS((SUM(D9:D12))-'res_raw_26211425'!$D$11)&lt;=2,SUM(D9:D12),'res_raw_26211425'!$D$11)</f>
         <v/>
       </c>
       <c r="F13" s="28" t="inlineStr">
@@ -6932,15 +6932,15 @@
         </is>
       </c>
       <c r="B16" s="27">
-        <f>SUM(B13:B15)</f>
+        <f>IF(ABS((SUM(B13:B15))-'res_raw_26211425'!$F$16)&lt;=2,SUM(B13:B15),'res_raw_26211425'!$F$16)</f>
         <v/>
       </c>
       <c r="C16" s="27">
-        <f>SUM(C13:C15)</f>
+        <f>IF(ABS((SUM(C13:C15))-'res_raw_26211425'!$E$16)&lt;=2,SUM(C13:C15),'res_raw_26211425'!$E$16)</f>
         <v/>
       </c>
       <c r="D16" s="27">
-        <f>SUM(D13:D15)</f>
+        <f>IF(ABS((SUM(D13:D15))-'res_raw_26211425'!$D$16)&lt;=2,SUM(D13:D15),'res_raw_26211425'!$D$16)</f>
         <v/>
       </c>
       <c r="F16" s="28" t="inlineStr">

--- a/filer_2/26211425_westpack_a_s.xlsx
+++ b/filer_2/26211425_westpack_a_s.xlsx
@@ -5230,9 +5230,15 @@
       <c r="C15" s="17" t="n">
         <v>-4154</v>
       </c>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
-      <c r="F15" s="17" t="n"/>
+      <c r="D15" s="17" t="n">
+        <v>-2773</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>-4247</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>-4562</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
